--- a/NY_State_Reports_2026-10-30/BetMGM_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-30/BetMGM_Weekly_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EBAB24-95CE-4106-9903-EBB249EA9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1326FE2D-27E4-4DAE-A416-1AF0759AA3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
@@ -3139,7 +3139,12 @@
         <v>46320</v>
       </c>
       <c r="B43" s="20"/>
-      <c r="F43" s="35"/>
+      <c r="C43" s="21">
+        <v>53128324.740000002</v>
+      </c>
+      <c r="F43" s="35">
+        <v>5212539.67</v>
+      </c>
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43"/>
@@ -3639,11 +3644,11 @@
       </c>
       <c r="C67" s="23">
         <f>SUM(C13:C66)</f>
-        <v>1057066855.25</v>
+        <v>1110195179.99</v>
       </c>
       <c r="F67" s="36">
         <f>SUM(F13:F66)</f>
-        <v>88294884.219999999</v>
+        <v>93507423.890000001</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
